--- a/data/trans_dic/POLIPATOLOGIA_5-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_5-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas</t>
+          <t>Población con cinco o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,94</t>
+          <t>1,24; 4,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,28</t>
+          <t>2,49; 7,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,73</t>
+          <t>2,61; 7,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,62</t>
+          <t>1,28; 4,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 10,03</t>
+          <t>3,45; 9,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,36</t>
+          <t>5,87; 13,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,89; 18,14</t>
+          <t>9,61; 18,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,15</t>
+          <t>4,1; 8,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,4</t>
+          <t>2,88; 6,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,25</t>
+          <t>4,79; 9,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 12,18</t>
+          <t>6,75; 11,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,49</t>
+          <t>3,08; 5,57</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,23</t>
+          <t>1,77; 5,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,62</t>
+          <t>3,12; 7,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,97</t>
+          <t>0,72; 3,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,17</t>
+          <t>3,72; 8,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 14,4</t>
+          <t>8,96; 14,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,26</t>
+          <t>7,17; 12,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,41</t>
+          <t>4,03; 8,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 16,21</t>
+          <t>11,54; 16,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,13</t>
+          <t>5,75; 9,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 9,02</t>
+          <t>5,78; 9,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,21</t>
+          <t>2,66; 5,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,54</t>
+          <t>8,19; 11,65</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,9</t>
+          <t>0,3; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,92</t>
+          <t>1,25; 5,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,45</t>
+          <t>0,53; 3,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 15,7</t>
+          <t>9,24; 15,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,79</t>
+          <t>0,98; 4,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 12,3</t>
+          <t>5,68; 11,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 9,69</t>
+          <t>3,71; 9,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 20,44</t>
+          <t>14,35; 20,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,05</t>
+          <t>0,97; 3,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,85</t>
+          <t>4,02; 7,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,87</t>
+          <t>2,55; 5,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 17,16</t>
+          <t>12,69; 17,19</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,87</t>
+          <t>1,23; 4,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,44</t>
+          <t>2,36; 6,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,06</t>
+          <t>3,21; 7,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 14,47</t>
+          <t>7,82; 14,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,47</t>
+          <t>2,67; 6,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 18,37</t>
+          <t>11,12; 17,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,33</t>
+          <t>10,03; 17,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 16,86</t>
+          <t>8,03; 17,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,12</t>
+          <t>2,17; 4,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 11,4</t>
+          <t>7,26; 11,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,86</t>
+          <t>7,33; 11,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,02; 14,84</t>
+          <t>8,95; 14,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,41</t>
+          <t>0,84; 5,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 13,41</t>
+          <t>5,22; 13,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,11</t>
+          <t>2,31; 8,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,58</t>
+          <t>6,46; 13,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 10,03</t>
+          <t>2,36; 8,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 23,54</t>
+          <t>12,42; 23,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 15,12</t>
+          <t>6,99; 15,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,57; 19,39</t>
+          <t>7,99; 19,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,97</t>
+          <t>2,2; 6,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,78; 17,06</t>
+          <t>10,29; 17,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 10,12</t>
+          <t>5,29; 10,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 15,61</t>
+          <t>8,91; 15,81</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,71</t>
+          <t>2,96; 8,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,47</t>
+          <t>1,95; 6,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,65; 20,47</t>
+          <t>13,75; 20,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,6</t>
+          <t>2,07; 7,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,1</t>
+          <t>4,04; 10,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,3</t>
+          <t>4,07; 10,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,94; 31,95</t>
+          <t>23,93; 31,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,5</t>
+          <t>1,19; 3,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,99</t>
+          <t>4,01; 7,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,25</t>
+          <t>3,45; 7,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,53; 24,94</t>
+          <t>19,6; 24,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,94</t>
+          <t>2,04; 4,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,82</t>
+          <t>1,98; 4,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,99</t>
+          <t>2,77; 6,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,93</t>
+          <t>7,47; 12,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,78</t>
+          <t>4,07; 7,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 12,61</t>
+          <t>7,79; 12,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,46; 13,2</t>
+          <t>8,58; 13,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,07; 67,27</t>
+          <t>21,72; 70,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,72</t>
+          <t>3,55; 5,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,13</t>
+          <t>5,31; 8,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,24</t>
+          <t>6,14; 9,11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,71; 56,8</t>
+          <t>15,7; 53,56</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,99</t>
+          <t>5,33; 8,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,92</t>
+          <t>1,08; 3,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,91</t>
+          <t>2,29; 4,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,07</t>
+          <t>2,05; 6,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,34</t>
+          <t>6,87; 11,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,3</t>
+          <t>6,43; 10,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,77; 13,28</t>
+          <t>8,75; 13,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,42; 16,02</t>
+          <t>11,25; 15,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,44</t>
+          <t>6,68; 9,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,2</t>
+          <t>4,07; 6,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,91</t>
+          <t>5,99; 8,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,37; 10,4</t>
+          <t>5,55; 10,69</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,12</t>
+          <t>2,89; 4,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,49</t>
+          <t>3,12; 4,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,2</t>
+          <t>2,93; 4,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,95</t>
+          <t>6,21; 9,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,71</t>
+          <t>5,91; 7,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,81; 10,91</t>
+          <t>8,9; 10,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,75; 10,9</t>
+          <t>8,81; 11,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,76; 35,55</t>
+          <t>15,75; 35,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,61; 5,69</t>
+          <t>4,57; 5,62</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6,25; 7,5</t>
+          <t>6,28; 7,47</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,33</t>
+          <t>6,1; 7,35</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,61; 23,57</t>
+          <t>11,72; 22,67</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas</t>
+          <t>Población con cinco o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3552; 13488</t>
+          <t>3380; 13394</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6560; 21452</t>
+          <t>7325; 22308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7972; 22696</t>
+          <t>7665; 22938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3926; 14389</t>
+          <t>3996; 14304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9392; 26149</t>
+          <t>9004; 26001</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17180; 38374</t>
+          <t>16862; 38595</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28553; 52382</t>
+          <t>27754; 52791</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12319; 23599</t>
+          <t>11886; 23305</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14910; 34178</t>
+          <t>15362; 34022</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28008; 53851</t>
+          <t>27899; 54222</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40966; 70925</t>
+          <t>39291; 68648</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18122; 33007</t>
+          <t>18490; 33473</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8412; 25791</t>
+          <t>8744; 24968</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15647; 38510</t>
+          <t>15747; 37162</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3463; 14931</t>
+          <t>3638; 15124</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20086; 42337</t>
+          <t>19303; 42059</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45508; 72581</t>
+          <t>45169; 72848</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36368; 64194</t>
+          <t>37567; 64809</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20560; 43990</t>
+          <t>21092; 44203</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59091; 83469</t>
+          <t>59433; 85584</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58340; 91043</t>
+          <t>57344; 91365</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58708; 92807</t>
+          <t>59519; 93805</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27029; 53420</t>
+          <t>27234; 52835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83773; 119282</t>
+          <t>84621; 120401</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>946; 9259</t>
+          <t>943; 8603</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4015; 19186</t>
+          <t>4035; 17947</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2355; 10996</t>
+          <t>1677; 10477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28994; 49625</t>
+          <t>29190; 48821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3434; 16063</t>
+          <t>3276; 15449</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19214; 41937</t>
+          <t>19358; 40436</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12482; 32601</t>
+          <t>12488; 31864</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50221; 71358</t>
+          <t>50083; 71991</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6491; 19938</t>
+          <t>6349; 20493</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27009; 52231</t>
+          <t>26757; 52073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16633; 38432</t>
+          <t>16719; 37158</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85514; 114164</t>
+          <t>84380; 114339</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4377; 17481</t>
+          <t>4402; 17784</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8477; 24102</t>
+          <t>8839; 24773</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11961; 29826</t>
+          <t>11890; 29528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23832; 45222</t>
+          <t>24452; 45381</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9283; 24052</t>
+          <t>9928; 24773</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43702; 71451</t>
+          <t>43251; 69500</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38942; 67105</t>
+          <t>38855; 67082</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37245; 80225</t>
+          <t>38218; 81927</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16231; 37364</t>
+          <t>15875; 35638</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54223; 86971</t>
+          <t>55422; 90538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55094; 89828</t>
+          <t>55517; 88807</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71078; 116951</t>
+          <t>70530; 116250</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1736; 10996</t>
+          <t>1713; 10884</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10705; 28503</t>
+          <t>11090; 28337</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4734; 17122</t>
+          <t>4880; 17313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12126; 24269</t>
+          <t>11548; 23382</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5319; 20823</t>
+          <t>4908; 18613</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28052; 51689</t>
+          <t>27268; 51741</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15134; 33054</t>
+          <t>15275; 33857</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19592; 50187</t>
+          <t>20680; 50413</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8891; 24528</t>
+          <t>9028; 26362</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42266; 73750</t>
+          <t>44454; 75607</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22763; 43478</t>
+          <t>22736; 45512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36046; 68311</t>
+          <t>38994; 69191</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1947</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7230; 21131</t>
+          <t>8109; 22933</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4978; 17012</t>
+          <t>5131; 17712</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36800; 55205</t>
+          <t>37062; 55729</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6399; 21147</t>
+          <t>5760; 20792</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11295; 28282</t>
+          <t>11316; 28622</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11198; 28128</t>
+          <t>11121; 28757</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>61546; 82119</t>
+          <t>61525; 82228</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5648; 19235</t>
+          <t>6533; 20804</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22416; 44240</t>
+          <t>22241; 44210</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18747; 38882</t>
+          <t>18491; 39780</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>102884; 131335</t>
+          <t>103222; 131024</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13402; 30355</t>
+          <t>12547; 30537</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13257; 31965</t>
+          <t>13149; 31922</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17858; 39346</t>
+          <t>18168; 40277</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45252; 74465</t>
+          <t>46613; 76826</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26609; 49664</t>
+          <t>25997; 49352</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53523; 87472</t>
+          <t>54049; 86593</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58484; 91254</t>
+          <t>59290; 92523</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>187449; 571307</t>
+          <t>184477; 601732</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>43887; 71645</t>
+          <t>44471; 73348</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70600; 110343</t>
+          <t>72066; 110442</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82835; 124528</t>
+          <t>82713; 122833</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>231564; 836972</t>
+          <t>231277; 789297</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>40729; 66837</t>
+          <t>39646; 66741</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7709; 22774</t>
+          <t>8386; 23985</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17893; 38234</t>
+          <t>17795; 38138</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19844; 65615</t>
+          <t>19061; 64743</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>53803; 88814</t>
+          <t>53818; 87086</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51287; 84885</t>
+          <t>52999; 83886</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72442; 109715</t>
+          <t>72252; 111331</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>81954; 115015</t>
+          <t>80754; 112574</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>98793; 144123</t>
+          <t>101975; 142098</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>64063; 99412</t>
+          <t>65273; 100159</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>96221; 143059</t>
+          <t>96169; 140904</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>88407; 171277</t>
+          <t>91309; 176058</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>92695; 134837</t>
+          <t>94626; 136121</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>107465; 153734</t>
+          <t>106968; 156398</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97702; 142580</t>
+          <t>99319; 143874</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>215175; 309745</t>
+          <t>214747; 311928</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>198422; 260679</t>
+          <t>199560; 258014</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>313531; 388151</t>
+          <t>316576; 388206</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>310099; 386289</t>
+          <t>312428; 390815</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>585192; 1319657</t>
+          <t>584704; 1318188</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>306644; 378429</t>
+          <t>303891; 374096</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>436314; 523549</t>
+          <t>438667; 522074</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>420266; 508712</t>
+          <t>422978; 509744</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>832624; 1690428</t>
+          <t>840275; 1625930</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_5-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_5-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,91</t>
+          <t>1,23; 4,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,57</t>
+          <t>2,27; 7,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,81</t>
+          <t>2,69; 7,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,59</t>
+          <t>1,21; 4,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,97</t>
+          <t>3,78; 10,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 13,44</t>
+          <t>5,69; 13,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 18,29</t>
+          <t>9,53; 18,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,05</t>
+          <t>4,35; 7,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,37</t>
+          <t>2,79; 6,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,32</t>
+          <t>4,75; 9,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,79</t>
+          <t>6,96; 11,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,57</t>
+          <t>3,11; 5,56</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,06</t>
+          <t>1,64; 5,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,35</t>
+          <t>3,1; 7,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,01</t>
+          <t>0,69; 2,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,11</t>
+          <t>4,14; 8,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 14,46</t>
+          <t>8,82; 14,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 12,37</t>
+          <t>7,05; 12,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,45</t>
+          <t>3,82; 8,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,62</t>
+          <t>11,17; 16,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,16</t>
+          <t>5,82; 9,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,11</t>
+          <t>5,79; 9,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,15</t>
+          <t>2,59; 5,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 11,65</t>
+          <t>8,19; 11,56</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,7</t>
+          <t>0,29; 2,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,54</t>
+          <t>1,24; 5,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,29</t>
+          <t>0,54; 3,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,24; 15,45</t>
+          <t>9,87; 16,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,61</t>
+          <t>1,17; 4,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 11,86</t>
+          <t>5,61; 11,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 9,47</t>
+          <t>3,8; 9,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,35; 20,62</t>
+          <t>14,24; 20,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,13</t>
+          <t>1,01; 3,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,83</t>
+          <t>4,04; 7,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,67</t>
+          <t>2,61; 5,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,69; 17,19</t>
+          <t>12,91; 17,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,96</t>
+          <t>1,21; 4,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,62</t>
+          <t>2,38; 6,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,98</t>
+          <t>3,36; 7,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 14,52</t>
+          <t>7,14; 13,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,67</t>
+          <t>2,63; 6,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 17,87</t>
+          <t>10,8; 17,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 17,32</t>
+          <t>10,0; 17,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 17,22</t>
+          <t>13,55; 19,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,88</t>
+          <t>2,2; 4,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 11,87</t>
+          <t>7,28; 11,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,73</t>
+          <t>7,52; 11,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 14,75</t>
+          <t>11,03; 14,88</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,35</t>
+          <t>0,84; 5,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 13,33</t>
+          <t>5,18; 13,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,2</t>
+          <t>2,3; 8,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 13,08</t>
+          <t>6,27; 12,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,96</t>
+          <t>2,4; 9,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,42; 23,56</t>
+          <t>13,1; 23,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 15,49</t>
+          <t>6,93; 15,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 19,48</t>
+          <t>14,06; 20,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,41</t>
+          <t>1,91; 6,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,29; 17,49</t>
+          <t>10,21; 16,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 10,59</t>
+          <t>5,29; 10,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,91; 15,81</t>
+          <t>11,26; 15,63</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,37</t>
+          <t>2,64; 7,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,73</t>
+          <t>1,85; 6,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,75; 20,67</t>
+          <t>13,37; 20,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,48</t>
+          <t>2,37; 7,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,22</t>
+          <t>4,38; 10,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 10,53</t>
+          <t>3,78; 10,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,93; 31,99</t>
+          <t>24,07; 32,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,79</t>
+          <t>1,18; 3,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,98</t>
+          <t>3,95; 8,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,42</t>
+          <t>3,49; 7,3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,6; 24,88</t>
+          <t>19,91; 25,07</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,97</t>
+          <t>2,02; 4,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,82</t>
+          <t>1,98; 4,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,13</t>
+          <t>2,79; 5,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,31</t>
+          <t>7,22; 11,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,73</t>
+          <t>4,08; 7,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,48</t>
+          <t>7,7; 12,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,58; 13,38</t>
+          <t>8,41; 13,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,72; 70,85</t>
+          <t>20,09; 25,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,55; 5,85</t>
+          <t>3,4; 5,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 8,14</t>
+          <t>5,24; 8,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 9,11</t>
+          <t>6,31; 9,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,7; 53,56</t>
+          <t>14,49; 18,08</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,97</t>
+          <t>5,45; 9,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,08</t>
+          <t>0,97; 3,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,9</t>
+          <t>2,26; 5,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,97</t>
+          <t>5,0; 8,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,11</t>
+          <t>6,95; 11,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,18</t>
+          <t>6,14; 10,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,75; 13,48</t>
+          <t>8,74; 13,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,68</t>
+          <t>10,65; 14,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,68; 9,3</t>
+          <t>6,66; 9,24</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,25</t>
+          <t>4,02; 6,27</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,78</t>
+          <t>5,99; 8,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 10,69</t>
+          <t>8,32; 10,73</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,15</t>
+          <t>2,82; 4,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,56</t>
+          <t>3,13; 4,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,24</t>
+          <t>2,88; 4,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,02</t>
+          <t>7,62; 9,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,64</t>
+          <t>5,89; 7,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,9; 10,91</t>
+          <t>8,94; 11,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,81; 11,03</t>
+          <t>8,71; 10,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,75; 35,51</t>
+          <t>15,45; 17,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,62</t>
+          <t>4,56; 5,65</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6,28; 7,47</t>
+          <t>6,29; 7,56</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,35</t>
+          <t>6,13; 7,34</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,72; 22,67</t>
+          <t>11,87; 13,22</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17255</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24847</t>
+          <t>26919</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3380; 13394</t>
+          <t>3345; 13195</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7325; 22308</t>
+          <t>6686; 21583</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7665; 22938</t>
+          <t>7899; 22800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3996; 14304</t>
+          <t>3873; 14505</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9004; 26001</t>
+          <t>9871; 26126</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16862; 38595</t>
+          <t>16353; 38263</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27754; 52791</t>
+          <t>27511; 52349</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11886; 23305</t>
+          <t>13744; 25103</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15362; 34022</t>
+          <t>14872; 33343</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27899; 54222</t>
+          <t>27633; 52703</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39291; 68648</t>
+          <t>40551; 69427</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18490; 33473</t>
+          <t>19759; 35308</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>31528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>70508</t>
+          <t>73960</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>100089</t>
+          <t>105487</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8744; 24968</t>
+          <t>8107; 25594</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15747; 37162</t>
+          <t>15647; 38322</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3638; 15124</t>
+          <t>3455; 13776</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19303; 42059</t>
+          <t>21970; 46257</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45169; 72848</t>
+          <t>44449; 73781</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37567; 64809</t>
+          <t>36946; 64474</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21092; 44203</t>
+          <t>19971; 43192</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59433; 85584</t>
+          <t>61053; 88279</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57344; 91365</t>
+          <t>58046; 90554</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59519; 93805</t>
+          <t>59612; 95193</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27234; 52835</t>
+          <t>26605; 51314</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>84621; 120401</t>
+          <t>88225; 124557</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38352</t>
+          <t>39561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60029</t>
+          <t>60792</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98381</t>
+          <t>100354</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>943; 8603</t>
+          <t>940; 8335</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4035; 17947</t>
+          <t>4032; 17027</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1677; 10477</t>
+          <t>1730; 10110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29190; 48821</t>
+          <t>31190; 51108</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3276; 15449</t>
+          <t>3915; 16029</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19358; 40436</t>
+          <t>19130; 40518</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12488; 31864</t>
+          <t>12793; 32964</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50083; 71991</t>
+          <t>50752; 72587</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6349; 20493</t>
+          <t>6631; 20564</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26757; 52073</t>
+          <t>26850; 51361</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16719; 37158</t>
+          <t>17062; 38551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84380; 114339</t>
+          <t>86825; 115936</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>36085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62668</t>
+          <t>66908</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96073</t>
+          <t>102993</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4402; 17784</t>
+          <t>4352; 17410</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8839; 24773</t>
+          <t>8918; 24555</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11890; 29528</t>
+          <t>12440; 28862</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24452; 45381</t>
+          <t>26635; 49081</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9928; 24773</t>
+          <t>9756; 24793</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43251; 69500</t>
+          <t>42000; 69216</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38855; 67082</t>
+          <t>38727; 68328</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38218; 81927</t>
+          <t>57175; 80431</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15875; 35638</t>
+          <t>16081; 35933</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55422; 90538</t>
+          <t>55556; 87046</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55517; 88807</t>
+          <t>56949; 89341</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70530; 116250</t>
+          <t>87712; 118281</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38630</t>
+          <t>39472</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>57612</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1713; 10884</t>
+          <t>1712; 10249</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11090; 28337</t>
+          <t>11009; 27632</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4880; 17313</t>
+          <t>4854; 16910</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11548; 23382</t>
+          <t>12897; 25113</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4908; 18613</t>
+          <t>4979; 20051</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27268; 51741</t>
+          <t>28777; 51393</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15275; 33857</t>
+          <t>15153; 34002</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20680; 50413</t>
+          <t>32187; 46676</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9028; 26362</t>
+          <t>7859; 24901</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44454; 75607</t>
+          <t>44121; 70953</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22736; 45512</t>
+          <t>22716; 43355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38994; 69191</t>
+          <t>48917; 67921</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45665</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>71473</t>
+          <t>73621</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>117138</t>
+          <t>119421</t>
         </is>
       </c>
     </row>
@@ -3254,57 +3254,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8109; 22933</t>
+          <t>7223; 21768</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5131; 17712</t>
+          <t>4855; 17039</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37062; 55729</t>
+          <t>36194; 55747</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5760; 20792</t>
+          <t>6582; 21150</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11316; 28622</t>
+          <t>12255; 28319</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11121; 28757</t>
+          <t>10319; 28011</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>61525; 82228</t>
+          <t>63494; 85453</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6533; 20804</t>
+          <t>6460; 19964</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22241; 44210</t>
+          <t>21895; 46043</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18491; 39780</t>
+          <t>18694; 39146</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>103222; 131024</t>
+          <t>106432; 134001</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58904</t>
+          <t>67465</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>352190</t>
+          <t>174948</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>411093</t>
+          <t>242413</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12547; 30537</t>
+          <t>12409; 29496</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13149; 31922</t>
+          <t>13117; 33034</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18168; 40277</t>
+          <t>18333; 38182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46613; 76826</t>
+          <t>51992; 83697</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25997; 49352</t>
+          <t>26028; 50837</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>54049; 86593</t>
+          <t>53436; 86161</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59290; 92523</t>
+          <t>58162; 90961</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>184477; 601732</t>
+          <t>155142; 197016</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44471; 73348</t>
+          <t>42648; 71456</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>72066; 110442</t>
+          <t>71023; 111519</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82713; 122833</t>
+          <t>85012; 124024</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>231277; 789297</t>
+          <t>216153; 269643</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>50100</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>95556</t>
+          <t>103717</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>140019</t>
+          <t>153817</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39646; 66741</t>
+          <t>40551; 67518</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8386; 23985</t>
+          <t>7563; 23952</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17795; 38138</t>
+          <t>17611; 39290</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19061; 64743</t>
+          <t>39868; 65350</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>53818; 87086</t>
+          <t>54439; 89170</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>52999; 83886</t>
+          <t>50593; 83676</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72252; 111331</t>
+          <t>72242; 109435</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>80754; 112574</t>
+          <t>88548; 119804</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>101975; 142098</t>
+          <t>101686; 141172</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65273; 100159</t>
+          <t>64414; 100443</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>96169; 140904</t>
+          <t>96139; 139420</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>91309; 176058</t>
+          <t>135603; 174816</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>275237</t>
+          <t>296611</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>768308</t>
+          <t>612406</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1043545</t>
+          <t>909017</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>94626; 136121</t>
+          <t>92334; 132324</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>106968; 156398</t>
+          <t>107358; 155302</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99319; 143874</t>
+          <t>97806; 141994</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>214747; 311928</t>
+          <t>269188; 326031</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>199560; 258014</t>
+          <t>198888; 259829</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>316576; 388206</t>
+          <t>318098; 393390</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>312428; 390815</t>
+          <t>308721; 386225</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>584704; 1318188</t>
+          <t>577420; 648180</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>303891; 374096</t>
+          <t>303623; 375812</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>438667; 522074</t>
+          <t>439319; 528206</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>422978; 509744</t>
+          <t>425038; 509279</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>840275; 1625930</t>
+          <t>863262; 960896</t>
         </is>
       </c>
     </row>
